--- a/data/output/sim_gridrnd/REL2/group_480_40/results/REL2_G2_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_480_40/results/REL2_G2_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,367 +466,422 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
@@ -840,10 +895,10 @@
         <v>479</v>
       </c>
       <c r="C2" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D2" t="n">
         <v>39</v>
-      </c>
-      <c r="D2" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E2" t="n">
         <v>479</v>
@@ -852,228 +907,261 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>471.023686319983</v>
-      </c>
-      <c r="J2" t="n">
-        <v>38.78993586344648</v>
-      </c>
-      <c r="K2" t="n">
-        <v>497.8988723751737</v>
-      </c>
-      <c r="L2" t="n">
-        <v>44.06908999849875</v>
-      </c>
-      <c r="M2" t="n">
-        <v>498.7439456030424</v>
-      </c>
-      <c r="N2" t="n">
-        <v>38.15742515486934</v>
-      </c>
-      <c r="O2" t="n">
-        <v>493.8111726568046</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40.22181545951383</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>492.9579982373961</v>
-      </c>
       <c r="R2" t="n">
-        <v>46.46405010454299</v>
+        <v>471.02</v>
       </c>
       <c r="S2" t="n">
-        <v>488.55698438223</v>
+        <v>38.79</v>
       </c>
       <c r="T2" t="n">
-        <v>47.18733619846387</v>
+        <v>497.9</v>
       </c>
       <c r="U2" t="n">
-        <v>488.1062433934732</v>
+        <v>44.07</v>
       </c>
       <c r="V2" t="n">
-        <v>43.63933560780836</v>
+        <v>498.74</v>
       </c>
       <c r="W2" t="n">
-        <v>485.142839598265</v>
+        <v>38.16</v>
       </c>
       <c r="X2" t="n">
-        <v>45.34626724611531</v>
+        <v>493.81</v>
       </c>
       <c r="Y2" t="n">
-        <v>484.9852982362652</v>
+        <v>40.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>45.52431059297672</v>
+        <v>492.96</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>46.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>488.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>47.19</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>488.11</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>43.64</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>485.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>45.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>484.99</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>45.52</v>
       </c>
       <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>492.175</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT2" t="n">
         <v>490.7666666666667</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AU2" t="n">
         <v>493.0375</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AV2" t="n">
         <v>493.68</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AW2" t="n">
         <v>492.6416666666667</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AX2" t="n">
         <v>489.2285714285715</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
         <v>486.4375</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AZ2" t="n">
         <v>484.9388888888889</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BA2" t="n">
         <v>484.55</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BB2" t="n">
         <v>83.38491695144872</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BC2" t="n">
         <v>72.37088886807703</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BD2" t="n">
         <v>65.62115583978996</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BE2" t="n">
         <v>61.08369340503241</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BF2" t="n">
         <v>59.28768784963329</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BG2" t="n">
         <v>60.60237417050623</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BH2" t="n">
         <v>61.4076224401336</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BI2" t="n">
         <v>60.64167652777061</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BJ2" t="n">
         <v>59.12027993844413</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BK2" t="n">
         <v>333</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BL2" t="n">
         <v>333</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BM2" t="n">
         <v>333</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BN2" t="n">
         <v>333</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BO2" t="n">
         <v>333</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BP2" t="n">
         <v>333</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BQ2" t="n">
         <v>333</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BR2" t="n">
         <v>333</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BS2" t="n">
         <v>333</v>
       </c>
-      <c r="BK2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>669</v>
-      </c>
       <c r="BT2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
         <v>0.625</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CD2" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="CE2" t="n">
         <v>0.7058823529411765</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="CF2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="CG2" t="n">
         <v>0.65625</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="CH2" t="n">
         <v>0.5121951219512195</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CI2" t="n">
         <v>0.4117647058823529</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CJ2" t="n">
         <v>0.360655737704918</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CK2" t="n">
         <v>0.373134328358209</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>484.99</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>45.52</v>
       </c>
     </row>
     <row r="3">
@@ -1086,10 +1174,10 @@
         <v>481</v>
       </c>
       <c r="C3" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D3" t="n">
         <v>42</v>
-      </c>
-      <c r="D3" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E3" t="n">
         <v>481</v>
@@ -1098,228 +1186,261 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>455.8536870780782</v>
-      </c>
-      <c r="J3" t="n">
-        <v>34.07872466481546</v>
-      </c>
-      <c r="K3" t="n">
-        <v>479.1913379831594</v>
-      </c>
-      <c r="L3" t="n">
-        <v>49.04102735503789</v>
-      </c>
-      <c r="M3" t="n">
-        <v>488.4428229519094</v>
-      </c>
-      <c r="N3" t="n">
-        <v>57.22765487615697</v>
-      </c>
-      <c r="O3" t="n">
-        <v>490.4493323477328</v>
-      </c>
-      <c r="P3" t="n">
-        <v>53.75826350346401</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>487.2875500227487</v>
-      </c>
       <c r="R3" t="n">
-        <v>54.4442917062251</v>
+        <v>455.85</v>
       </c>
       <c r="S3" t="n">
-        <v>489.2064073571436</v>
+        <v>34.08</v>
       </c>
       <c r="T3" t="n">
-        <v>55.61796254846253</v>
+        <v>479.19</v>
       </c>
       <c r="U3" t="n">
-        <v>487.4073660716326</v>
+        <v>49.04</v>
       </c>
       <c r="V3" t="n">
-        <v>54.42606025172067</v>
+        <v>488.44</v>
       </c>
       <c r="W3" t="n">
-        <v>492.068587107682</v>
+        <v>57.23</v>
       </c>
       <c r="X3" t="n">
-        <v>54.72975621865542</v>
+        <v>490.45</v>
       </c>
       <c r="Y3" t="n">
-        <v>492.4326763373622</v>
+        <v>53.76</v>
       </c>
       <c r="Z3" t="n">
-        <v>55.24258718595054</v>
+        <v>487.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>54.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>489.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>55.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>487.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>54.43</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>492.07</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>54.73</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>492.43</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>55.24</v>
       </c>
       <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>478.55</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AT3" t="n">
         <v>477.0166666666667</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AU3" t="n">
         <v>479.475</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AV3" t="n">
         <v>483.7</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AW3" t="n">
         <v>486.525</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AX3" t="n">
         <v>488.8</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AY3" t="n">
         <v>489.13125</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AZ3" t="n">
         <v>489.0166666666667</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="BA3" t="n">
         <v>489.615</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BB3" t="n">
         <v>81.94325780685071</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
         <v>73.34268690348222</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
         <v>70.82883858288233</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BE3" t="n">
         <v>71.21650089691293</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BF3" t="n">
         <v>70.87994103882048</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BG3" t="n">
         <v>71.38809424546925</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BH3" t="n">
         <v>70.54175375929847</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BI3" t="n">
         <v>68.9878793702198</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BJ3" t="n">
         <v>67.42526807510667</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BK3" t="n">
         <v>341</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BL3" t="n">
         <v>341</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BM3" t="n">
         <v>341</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BN3" t="n">
         <v>341</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>341</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BP3" t="n">
         <v>341</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BQ3" t="n">
         <v>341</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BR3" t="n">
         <v>341</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
         <v>341</v>
       </c>
-      <c r="BK3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>669</v>
-      </c>
       <c r="BT3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
         <v>1</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="CD3" t="n">
         <v>0.875</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="CE3" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BW3" t="n">
+      <c r="CF3" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BX3" t="n">
+      <c r="CG3" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BY3" t="n">
+      <c r="CH3" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CI3" t="n">
         <v>0.55</v>
       </c>
-      <c r="CA3" t="n">
+      <c r="CJ3" t="n">
         <v>0.5625</v>
       </c>
-      <c r="CB3" t="n">
+      <c r="CK3" t="n">
         <v>0.5471698113207547</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>492.43</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>55.24</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>481</v>
       </c>
       <c r="C4" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D4" t="n">
         <v>38</v>
-      </c>
-      <c r="D4" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E4" t="n">
         <v>481</v>
@@ -1344,228 +1465,261 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>462.3467223468301</v>
-      </c>
-      <c r="J4" t="n">
-        <v>40.61688508024216</v>
-      </c>
-      <c r="K4" t="n">
-        <v>474.7643596526866</v>
-      </c>
-      <c r="L4" t="n">
-        <v>51.12066358104762</v>
-      </c>
-      <c r="M4" t="n">
-        <v>478.1117377710165</v>
-      </c>
-      <c r="N4" t="n">
-        <v>49.1638739268999</v>
-      </c>
-      <c r="O4" t="n">
-        <v>476.0986608953896</v>
-      </c>
-      <c r="P4" t="n">
-        <v>47.70174902381991</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>475.9876084586238</v>
-      </c>
       <c r="R4" t="n">
-        <v>41.3937605177076</v>
+        <v>462.35</v>
       </c>
       <c r="S4" t="n">
-        <v>479.1387784031648</v>
+        <v>40.62</v>
       </c>
       <c r="T4" t="n">
-        <v>45.13003990078912</v>
+        <v>474.76</v>
       </c>
       <c r="U4" t="n">
-        <v>478.3051214727167</v>
+        <v>51.12</v>
       </c>
       <c r="V4" t="n">
-        <v>44.81049748413837</v>
+        <v>478.11</v>
       </c>
       <c r="W4" t="n">
-        <v>477.6423750074195</v>
+        <v>49.16</v>
       </c>
       <c r="X4" t="n">
-        <v>44.53229452310634</v>
+        <v>476.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>479.5923961147247</v>
+        <v>47.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.57957320923234</v>
+        <v>475.99</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>41.39</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>479.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>45.13</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>478.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>44.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>477.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>44.53</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>479.59</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>42.58</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>494.525</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>486.0833333333333</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>483.1625</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>482.79</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>481.6333333333333</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>481.9357142857143</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>483.63125</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>484.7333333333333</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>485.405</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>82.63231435098498</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>75.18738627958518</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>71.12092584992128</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>68.76733163355983</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>66.0199380658769</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>63.43604323752115</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>62.2911131176631</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>60.55168591101874</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>58.5721860186215</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>328</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>328</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>328</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>328</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>328</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>328</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>328</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>328</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>328</v>
       </c>
-      <c r="BK4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>669</v>
-      </c>
       <c r="BT4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.875</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.8529411764705882</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.6976744186046512</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>479.59</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>42.58</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>480</v>
       </c>
       <c r="C5" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D5" t="n">
         <v>42</v>
-      </c>
-      <c r="D5" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E5" t="n">
         <v>480</v>
@@ -1590,228 +1744,261 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>489.2701765290687</v>
-      </c>
-      <c r="J5" t="n">
-        <v>54.44222188910635</v>
-      </c>
-      <c r="K5" t="n">
-        <v>495.2762786433304</v>
-      </c>
-      <c r="L5" t="n">
-        <v>53.62423223638682</v>
-      </c>
-      <c r="M5" t="n">
-        <v>482.4487651375035</v>
-      </c>
-      <c r="N5" t="n">
-        <v>53.52840127981953</v>
-      </c>
-      <c r="O5" t="n">
-        <v>474.6546805477142</v>
-      </c>
-      <c r="P5" t="n">
-        <v>49.37019863752239</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>474.1310109402339</v>
-      </c>
       <c r="R5" t="n">
-        <v>50.81370347710317</v>
+        <v>489.27</v>
       </c>
       <c r="S5" t="n">
-        <v>476.3193662637657</v>
+        <v>54.44</v>
       </c>
       <c r="T5" t="n">
-        <v>50.2820039892686</v>
+        <v>495.28</v>
       </c>
       <c r="U5" t="n">
-        <v>479.214962531657</v>
+        <v>53.62</v>
       </c>
       <c r="V5" t="n">
-        <v>54.34870913195213</v>
+        <v>482.45</v>
       </c>
       <c r="W5" t="n">
-        <v>481.6803077403168</v>
+        <v>53.53</v>
       </c>
       <c r="X5" t="n">
-        <v>50.55058415261148</v>
+        <v>474.65</v>
       </c>
       <c r="Y5" t="n">
-        <v>480.4305091924656</v>
+        <v>49.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>51.41640815916734</v>
+        <v>474.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>50.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>476.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>50.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>479.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>54.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>481.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>50.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>480.43</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>51.42</v>
       </c>
       <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>516.55</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>508.4166666666667</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>505.3</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>502.22</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>498.9</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>493.9857142857143</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>491.7625</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>490.0166666666667</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>487.73</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>100.856816824645</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>87.18147579745494</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>78.65452943092343</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>73.04718748863641</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>69.50532353712197</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>69.04129051457807</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>68.79875430376629</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>68.06463227452763</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>68.09718863506775</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>319</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>319</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>319</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>319</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>319</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>319</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>319</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>319</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>319</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>706</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BU5" t="n">
         <v>706</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BV5" t="n">
         <v>706</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BW5" t="n">
         <v>706</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BX5" t="n">
         <v>706</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BY5" t="n">
         <v>706</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BZ5" t="n">
         <v>706</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="CA5" t="n">
         <v>706</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="CB5" t="n">
         <v>706</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="CC5" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>0.6190476190476191</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.8529411764705882</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>0.7435897435897436</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>0.9743589743589743</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>0.9285714285714286</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>480.43</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>51.42</v>
       </c>
     </row>
     <row r="6">
@@ -1824,10 +2011,10 @@
         <v>478</v>
       </c>
       <c r="C6" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D6" t="n">
         <v>42</v>
-      </c>
-      <c r="D6" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E6" t="n">
         <v>478</v>
@@ -1836,228 +2023,261 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>492.2172141333319</v>
-      </c>
-      <c r="J6" t="n">
-        <v>53.91958179029336</v>
-      </c>
-      <c r="K6" t="n">
-        <v>471.0851196896874</v>
-      </c>
-      <c r="L6" t="n">
-        <v>50.15924721851771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>479.0975077825616</v>
-      </c>
-      <c r="N6" t="n">
-        <v>43.60253944372558</v>
-      </c>
-      <c r="O6" t="n">
-        <v>470.8634093941463</v>
-      </c>
-      <c r="P6" t="n">
-        <v>47.48558737475575</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>470.7056781809648</v>
-      </c>
       <c r="R6" t="n">
-        <v>47.85366372906198</v>
+        <v>492.22</v>
       </c>
       <c r="S6" t="n">
-        <v>477.1774014265592</v>
+        <v>53.92</v>
       </c>
       <c r="T6" t="n">
-        <v>51.71085480914111</v>
+        <v>471.09</v>
       </c>
       <c r="U6" t="n">
-        <v>475.8940670619724</v>
+        <v>50.16</v>
       </c>
       <c r="V6" t="n">
-        <v>55.5664060796317</v>
+        <v>479.1</v>
       </c>
       <c r="W6" t="n">
-        <v>476.3016440744809</v>
+        <v>43.6</v>
       </c>
       <c r="X6" t="n">
-        <v>55.13732393368485</v>
+        <v>470.86</v>
       </c>
       <c r="Y6" t="n">
-        <v>479.0333323983964</v>
+        <v>47.49</v>
       </c>
       <c r="Z6" t="n">
-        <v>55.35163074246506</v>
+        <v>470.71</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>47.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>477.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>51.71</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>475.89</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>55.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>476.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>55.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>479.03</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>55.35</v>
       </c>
       <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>475.825</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AT6" t="n">
         <v>477.3166666666667</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AU6" t="n">
         <v>478.725</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AV6" t="n">
         <v>478.85</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AW6" t="n">
         <v>477.35</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AX6" t="n">
         <v>477.1857142857143</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AY6" t="n">
         <v>479.6</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AZ6" t="n">
         <v>481.3555555555556</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BA6" t="n">
         <v>482.37</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BB6" t="n">
         <v>89.94522986240015</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BC6" t="n">
         <v>81.13989804994553</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BD6" t="n">
         <v>74.68918512743328</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BE6" t="n">
         <v>70.02190728622007</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BF6" t="n">
         <v>67.68316506586652</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BG6" t="n">
         <v>65.95286040740285</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BH6" t="n">
         <v>66.66607083067068</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BI6" t="n">
         <v>67.22207162517566</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BJ6" t="n">
         <v>67.70135227600701</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BK6" t="n">
         <v>339</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BL6" t="n">
         <v>339</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BM6" t="n">
         <v>339</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BN6" t="n">
         <v>339</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BO6" t="n">
         <v>339</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BP6" t="n">
         <v>339</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BQ6" t="n">
         <v>339</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BR6" t="n">
         <v>339</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BS6" t="n">
         <v>339</v>
       </c>
-      <c r="BK6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>669</v>
-      </c>
       <c r="BT6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="CD6" t="n">
         <v>0.4736842105263158</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="CE6" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="CF6" t="n">
         <v>0.68</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="CG6" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CH6" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CI6" t="n">
         <v>0.8787878787878788</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CJ6" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CK6" t="n">
         <v>0.7857142857142857</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>479.03</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>55.35</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>482</v>
       </c>
       <c r="C7" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D7" t="n">
         <v>38</v>
-      </c>
-      <c r="D7" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E7" t="n">
         <v>482</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>467.0439155495097</v>
-      </c>
-      <c r="J7" t="n">
-        <v>57.54873817132864</v>
-      </c>
-      <c r="K7" t="n">
-        <v>481.7527192816407</v>
-      </c>
-      <c r="L7" t="n">
-        <v>53.21391001906817</v>
-      </c>
-      <c r="M7" t="n">
-        <v>484.895528482906</v>
-      </c>
-      <c r="N7" t="n">
-        <v>41.22148795363877</v>
-      </c>
-      <c r="O7" t="n">
-        <v>495.1475908446512</v>
-      </c>
-      <c r="P7" t="n">
-        <v>40.77652753594594</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>490.786374887766</v>
-      </c>
       <c r="R7" t="n">
-        <v>39.64846104253716</v>
+        <v>467.04</v>
       </c>
       <c r="S7" t="n">
-        <v>490.7967370794264</v>
+        <v>57.55</v>
       </c>
       <c r="T7" t="n">
-        <v>37.58331095927755</v>
+        <v>481.75</v>
       </c>
       <c r="U7" t="n">
-        <v>491.8034378468752</v>
+        <v>53.21</v>
       </c>
       <c r="V7" t="n">
-        <v>39.41939022321194</v>
+        <v>484.9</v>
       </c>
       <c r="W7" t="n">
-        <v>489.053779322689</v>
+        <v>41.22</v>
       </c>
       <c r="X7" t="n">
-        <v>38.58412282070004</v>
+        <v>495.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>489.9889517304712</v>
+        <v>40.78</v>
       </c>
       <c r="Z7" t="n">
-        <v>36.28342884439404</v>
+        <v>490.79</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>39.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>490.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>37.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>491.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>39.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>489.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>38.58</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>489.99</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>36.28</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>481.425</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>476.0666666666667</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>479.1375</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>482.81</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>483.8583333333333</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>484.5928571428572</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>485.14375</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>486.1111111111111</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>486.18</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>79.38636139161437</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>78.51026825977748</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>71.47617500783041</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>66.14902795960043</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>62.71553447024819</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>59.97926980317823</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>58.86518993375881</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>57.3189796847324</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>55.32411409141587</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>328</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>328</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>328</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>328</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>328</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>328</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>328</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>328</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>328</v>
       </c>
-      <c r="BK7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>669</v>
-      </c>
       <c r="BT7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.3</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.3</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.52</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.4857142857142857</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.4888888888888889</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.4791666666666667</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.5600000000000001</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>489.99</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>36.28</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>482</v>
       </c>
       <c r="C8" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D8" t="n">
         <v>39</v>
-      </c>
-      <c r="D8" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E8" t="n">
         <v>482</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>488.1071652840338</v>
-      </c>
-      <c r="J8" t="n">
-        <v>47.25035557915951</v>
-      </c>
-      <c r="K8" t="n">
-        <v>488.5876927352982</v>
-      </c>
-      <c r="L8" t="n">
-        <v>49.01510516900476</v>
-      </c>
-      <c r="M8" t="n">
-        <v>495.6619819964793</v>
-      </c>
-      <c r="N8" t="n">
-        <v>55.85523530836752</v>
-      </c>
-      <c r="O8" t="n">
-        <v>498.4238370749126</v>
-      </c>
-      <c r="P8" t="n">
-        <v>52.90269843283903</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>501.4938195796624</v>
-      </c>
       <c r="R8" t="n">
-        <v>51.75492285651639</v>
+        <v>488.11</v>
       </c>
       <c r="S8" t="n">
-        <v>497.2565852444084</v>
+        <v>47.25</v>
       </c>
       <c r="T8" t="n">
-        <v>49.3259138910942</v>
+        <v>488.59</v>
       </c>
       <c r="U8" t="n">
-        <v>494.0549712220975</v>
+        <v>49.02</v>
       </c>
       <c r="V8" t="n">
-        <v>46.86345803184923</v>
+        <v>495.66</v>
       </c>
       <c r="W8" t="n">
-        <v>490.9673083323081</v>
+        <v>55.86</v>
       </c>
       <c r="X8" t="n">
-        <v>46.46030141480337</v>
+        <v>498.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>491.8293584740353</v>
+        <v>52.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>44.97176234508865</v>
+        <v>501.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>51.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>497.26</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>49.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>494.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>46.86</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>490.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>46.46</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>491.83</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>44.97</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>489.3</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>489.2666666666667</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>489.025</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>490.28</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>492.4083333333334</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>493.5571428571429</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>492.925</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>494.2388888888889</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>495</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>81.49423292479045</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>74.11317171881272</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>70.33011001697638</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>68.59549256328728</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>68.28585698289865</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>67.11602655408143</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>64.07978913042707</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>62.37933809353586</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>60.98844152788297</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>329</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>329</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>329</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>329</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>329</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>329</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>329</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>329</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>329</v>
       </c>
-      <c r="BK8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>669</v>
-      </c>
       <c r="BT8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
         <v>0.9</v>
       </c>
-      <c r="BU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW8" t="n">
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
         <v>0.7096774193548387</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.8387096774193549</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.9705882352941176</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.9714285714285714</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.9714285714285714</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.9714285714285714</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>491.83</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>44.97</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>482</v>
       </c>
       <c r="C9" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D9" t="n">
         <v>40</v>
-      </c>
-      <c r="D9" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E9" t="n">
         <v>482</v>
@@ -2574,244 +2860,277 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>469.420601515048</v>
-      </c>
-      <c r="J9" t="n">
-        <v>32.85997659493119</v>
-      </c>
-      <c r="K9" t="n">
-        <v>484.1980764928066</v>
-      </c>
-      <c r="L9" t="n">
-        <v>32.32226178974355</v>
-      </c>
-      <c r="M9" t="n">
-        <v>481.5243782483797</v>
-      </c>
-      <c r="N9" t="n">
-        <v>37.52551306631158</v>
-      </c>
-      <c r="O9" t="n">
-        <v>474.2693951522972</v>
-      </c>
-      <c r="P9" t="n">
-        <v>47.74331244488457</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>472.8134568385164</v>
-      </c>
       <c r="R9" t="n">
-        <v>54.37715950262843</v>
+        <v>469.42</v>
       </c>
       <c r="S9" t="n">
-        <v>473.5103410323666</v>
+        <v>32.86</v>
       </c>
       <c r="T9" t="n">
-        <v>52.86303803569075</v>
+        <v>484.2</v>
       </c>
       <c r="U9" t="n">
-        <v>473.1853873153051</v>
+        <v>32.32</v>
       </c>
       <c r="V9" t="n">
-        <v>50.97511955400517</v>
+        <v>481.52</v>
       </c>
       <c r="W9" t="n">
-        <v>476.7527370102426</v>
+        <v>37.53</v>
       </c>
       <c r="X9" t="n">
-        <v>48.53479487153788</v>
+        <v>474.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>478.9061385198903</v>
+        <v>47.74</v>
       </c>
       <c r="Z9" t="n">
-        <v>47.96123431337917</v>
+        <v>472.81</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>54.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>473.51</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>52.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>473.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>50.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>476.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>48.53</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>478.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>47.96</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>480.95</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>478.5</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>480.0375</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>479.68</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>479.425</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>479.1071428571428</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>479.49375</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>479.7555555555555</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>480.495</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>77.2363094664679</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>68.16414013247729</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>61.54275825594754</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>58.60663443672568</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>57.62026010874994</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>56.99357061841918</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>56.91506796040483</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>56.63073588532627</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>56.47114285190268</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>330</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>330</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>330</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>330</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>330</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>330</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>330</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>330</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>330</v>
       </c>
-      <c r="BK9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>669</v>
-      </c>
       <c r="BT9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.4722222222222222</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.5581395348837209</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.5686274509803921</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.6078431372549019</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.6545454545454545</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.7017543859649122</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>478.91</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>47.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S11_G2_480_38_REL2</t>
+          <t>S09_G2_480_41_REL2</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>480</v>
       </c>
       <c r="C10" t="n">
-        <v>38</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D10" t="n">
-        <v>56.33802816901409</v>
+        <v>41</v>
       </c>
       <c r="E10" t="n">
         <v>480</v>
@@ -2820,720 +3139,819 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>468.7966831569726</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24.80508075239359</v>
-      </c>
-      <c r="K10" t="n">
-        <v>467.9347732763723</v>
-      </c>
-      <c r="L10" t="n">
-        <v>30.1981889786255</v>
-      </c>
-      <c r="M10" t="n">
-        <v>464.6901265522332</v>
-      </c>
-      <c r="N10" t="n">
-        <v>39.90364708960092</v>
-      </c>
-      <c r="O10" t="n">
-        <v>467.8678260819503</v>
-      </c>
-      <c r="P10" t="n">
-        <v>40.07782511633464</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>464.9806379315854</v>
-      </c>
       <c r="R10" t="n">
-        <v>44.51132929462521</v>
+        <v>464.37</v>
       </c>
       <c r="S10" t="n">
-        <v>467.4230004473719</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>44.36413810991991</v>
+        <v>456.76</v>
       </c>
       <c r="U10" t="n">
-        <v>469.0345460898827</v>
+        <v>62.36</v>
       </c>
       <c r="V10" t="n">
-        <v>46.07559655925728</v>
+        <v>454.92</v>
       </c>
       <c r="W10" t="n">
-        <v>474.0441787176674</v>
+        <v>52.02</v>
       </c>
       <c r="X10" t="n">
-        <v>47.82381179523441</v>
+        <v>459.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>475.0721569338708</v>
+        <v>46.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>47.85686036335971</v>
+        <v>464.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>43.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>464.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>44.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>467.86</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>42.64</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>469.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>46.51</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>469.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>487.4</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>480.0666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>476.65</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>475.4</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>475.0416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>474.5571428571429</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>475.5125</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>479.0777777777778</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>482.04</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>70.90479532443486</v>
+        <v>484.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>63.46307762961251</v>
+        <v>481.0333333333334</v>
       </c>
       <c r="AU10" t="n">
-        <v>59.55944509479584</v>
+        <v>477.4625</v>
       </c>
       <c r="AV10" t="n">
-        <v>58.91247745596853</v>
+        <v>474.76</v>
       </c>
       <c r="AW10" t="n">
-        <v>58.30585960166344</v>
+        <v>472.0833333333333</v>
       </c>
       <c r="AX10" t="n">
-        <v>58.17489289431744</v>
+        <v>470.9714285714286</v>
       </c>
       <c r="AY10" t="n">
-        <v>58.25407576942579</v>
+        <v>471.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>59.49691453769827</v>
+        <v>472.9833333333333</v>
       </c>
       <c r="BA10" t="n">
-        <v>59.80023745772252</v>
+        <v>474.755</v>
       </c>
       <c r="BB10" t="n">
-        <v>330</v>
+        <v>89.27814682216471</v>
       </c>
       <c r="BC10" t="n">
-        <v>330</v>
+        <v>83.16128239083912</v>
       </c>
       <c r="BD10" t="n">
-        <v>330</v>
+        <v>79.37756984028927</v>
       </c>
       <c r="BE10" t="n">
-        <v>330</v>
+        <v>74.87177305233261</v>
       </c>
       <c r="BF10" t="n">
-        <v>330</v>
+        <v>72.04091237314776</v>
       </c>
       <c r="BG10" t="n">
-        <v>330</v>
+        <v>69.28285119268516</v>
       </c>
       <c r="BH10" t="n">
-        <v>330</v>
+        <v>66.25952761678882</v>
       </c>
       <c r="BI10" t="n">
-        <v>330</v>
+        <v>64.27704575593927</v>
       </c>
       <c r="BJ10" t="n">
-        <v>330</v>
+        <v>62.77368059147082</v>
       </c>
       <c r="BK10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BL10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BM10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BN10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BO10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BP10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BQ10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BR10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BS10" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.4444444444444444</v>
+        <v>669</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.8928571428571429</v>
+        <v>669</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.9333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.7567567567567568</v>
+        <v>669</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.7567567567567568</v>
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>45.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S09_G2_480_41_REL2</t>
+          <t>S10_G2_481_38_REL2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D11" t="n">
-        <v>60.78576723498888</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>464.3680615097534</v>
-      </c>
-      <c r="J11" t="n">
-        <v>64.67667762161919</v>
-      </c>
-      <c r="K11" t="n">
-        <v>456.7645200096611</v>
-      </c>
-      <c r="L11" t="n">
-        <v>62.35629535293253</v>
-      </c>
-      <c r="M11" t="n">
-        <v>454.9190358178021</v>
-      </c>
-      <c r="N11" t="n">
-        <v>52.02061265401875</v>
-      </c>
-      <c r="O11" t="n">
-        <v>459.8539078700745</v>
-      </c>
-      <c r="P11" t="n">
-        <v>46.35660664205206</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>464.4226537856761</v>
-      </c>
       <c r="R11" t="n">
-        <v>43.8620396739668</v>
+        <v>480.27</v>
       </c>
       <c r="S11" t="n">
-        <v>464.5151253930444</v>
+        <v>45.18</v>
       </c>
       <c r="T11" t="n">
-        <v>44.17494370226468</v>
+        <v>475.97</v>
       </c>
       <c r="U11" t="n">
-        <v>467.8550926813475</v>
+        <v>49.64</v>
       </c>
       <c r="V11" t="n">
-        <v>42.64232123078556</v>
+        <v>466.68</v>
       </c>
       <c r="W11" t="n">
-        <v>469.2962122155092</v>
+        <v>51.83</v>
       </c>
       <c r="X11" t="n">
-        <v>46.50813158980881</v>
+        <v>474.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>469.4968006709368</v>
+        <v>51.96</v>
       </c>
       <c r="Z11" t="n">
-        <v>45.49721337573129</v>
+        <v>481.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>48.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>483.93</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>51.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>484.75</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>47.01</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>485.37</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>487.16</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>47.41</v>
       </c>
       <c r="AJ11" t="n">
-        <v>484.25</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>481.0333333333334</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>477.4625</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>474.76</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>472.0833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>470.9714285714286</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>471.25</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>472.9833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>474.755</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>89.27814682216471</v>
+        <v>490.425</v>
       </c>
       <c r="AT11" t="n">
-        <v>83.16128239083912</v>
+        <v>487.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>79.37756984028927</v>
+        <v>485.8125</v>
       </c>
       <c r="AV11" t="n">
-        <v>74.87177305233261</v>
+        <v>484.16</v>
       </c>
       <c r="AW11" t="n">
-        <v>72.04091237314776</v>
+        <v>484.1</v>
       </c>
       <c r="AX11" t="n">
-        <v>69.28285119268516</v>
+        <v>484.4428571428571</v>
       </c>
       <c r="AY11" t="n">
-        <v>66.25952761678882</v>
+        <v>486.10625</v>
       </c>
       <c r="AZ11" t="n">
-        <v>64.27704575593927</v>
+        <v>487.3166666666667</v>
       </c>
       <c r="BA11" t="n">
-        <v>62.77368059147082</v>
+        <v>488.31</v>
       </c>
       <c r="BB11" t="n">
-        <v>338</v>
+        <v>85.01143673059526</v>
       </c>
       <c r="BC11" t="n">
-        <v>338</v>
+        <v>76.3320596691412</v>
       </c>
       <c r="BD11" t="n">
-        <v>338</v>
+        <v>71.96268021516431</v>
       </c>
       <c r="BE11" t="n">
-        <v>338</v>
+        <v>69.06398772153256</v>
       </c>
       <c r="BF11" t="n">
-        <v>338</v>
+        <v>66.3864192939088</v>
       </c>
       <c r="BG11" t="n">
-        <v>338</v>
+        <v>64.11922727327934</v>
       </c>
       <c r="BH11" t="n">
-        <v>338</v>
+        <v>61.62726637566768</v>
       </c>
       <c r="BI11" t="n">
-        <v>338</v>
+        <v>59.20852744514275</v>
       </c>
       <c r="BJ11" t="n">
-        <v>338</v>
+        <v>57.16234687274483</v>
       </c>
       <c r="BK11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BL11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BM11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BN11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BO11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BP11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BQ11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BR11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BS11" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.8235294117647058</v>
+        <v>669</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.9545454545454546</v>
+        <v>669</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.7241379310344828</v>
+        <v>669</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.967741935483871</v>
+        <v>669</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.7111111111111111</v>
+        <v>669</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7111111111111111</v>
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.7173913043478261</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.7173913043478261</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.7173913043478261</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>487.16</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>47.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S10_G2_481_38_REL2</t>
+          <t>S11_G2_480_38_REL2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C12" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D12" t="n">
         <v>38</v>
       </c>
-      <c r="D12" t="n">
-        <v>56.33802816901409</v>
-      </c>
       <c r="E12" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F12" t="n">
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>480.2667584325163</v>
-      </c>
-      <c r="J12" t="n">
-        <v>45.17730044265574</v>
-      </c>
-      <c r="K12" t="n">
-        <v>475.9680017023583</v>
-      </c>
-      <c r="L12" t="n">
-        <v>49.64476166092687</v>
-      </c>
-      <c r="M12" t="n">
-        <v>466.683728454612</v>
-      </c>
-      <c r="N12" t="n">
-        <v>51.82635056225912</v>
-      </c>
-      <c r="O12" t="n">
-        <v>474.7664027012527</v>
-      </c>
-      <c r="P12" t="n">
-        <v>51.96005759318646</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>481.0526547096115</v>
-      </c>
       <c r="R12" t="n">
-        <v>48.6254623631166</v>
+        <v>468.8</v>
       </c>
       <c r="S12" t="n">
-        <v>483.9260515054564</v>
+        <v>24.81</v>
       </c>
       <c r="T12" t="n">
-        <v>51.72337154483549</v>
+        <v>467.93</v>
       </c>
       <c r="U12" t="n">
-        <v>484.7521311036883</v>
+        <v>30.2</v>
       </c>
       <c r="V12" t="n">
-        <v>47.00999490288176</v>
+        <v>464.69</v>
       </c>
       <c r="W12" t="n">
-        <v>485.3690458331456</v>
+        <v>39.9</v>
       </c>
       <c r="X12" t="n">
-        <v>46.50297421487998</v>
+        <v>467.87</v>
       </c>
       <c r="Y12" t="n">
-        <v>487.1632448911165</v>
+        <v>40.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>47.41158198946707</v>
+        <v>464.98</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>44.51</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>467.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>44.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>469.03</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>46.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>474.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>47.82</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>475.07</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>47.86</v>
       </c>
       <c r="AJ12" t="n">
-        <v>490.425</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>487.5</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>485.8125</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>484.16</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>484.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>484.4428571428571</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>486.10625</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>487.3166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>488.31</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>85.01143673059526</v>
+        <v>487.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>76.3320596691412</v>
+        <v>480.0666666666667</v>
       </c>
       <c r="AU12" t="n">
-        <v>71.96268021516431</v>
+        <v>476.65</v>
       </c>
       <c r="AV12" t="n">
-        <v>69.06398772153256</v>
+        <v>475.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>66.3864192939088</v>
+        <v>475.0416666666667</v>
       </c>
       <c r="AX12" t="n">
-        <v>64.11922727327934</v>
+        <v>474.5571428571429</v>
       </c>
       <c r="AY12" t="n">
-        <v>61.62726637566768</v>
+        <v>475.5125</v>
       </c>
       <c r="AZ12" t="n">
-        <v>59.20852744514275</v>
+        <v>479.0777777777778</v>
       </c>
       <c r="BA12" t="n">
-        <v>57.16234687274483</v>
+        <v>482.04</v>
       </c>
       <c r="BB12" t="n">
-        <v>329</v>
+        <v>70.90479532443486</v>
       </c>
       <c r="BC12" t="n">
-        <v>329</v>
+        <v>63.46307762961251</v>
       </c>
       <c r="BD12" t="n">
-        <v>329</v>
+        <v>59.55944509479584</v>
       </c>
       <c r="BE12" t="n">
-        <v>329</v>
+        <v>58.91247745596853</v>
       </c>
       <c r="BF12" t="n">
-        <v>329</v>
+        <v>58.30585960166344</v>
       </c>
       <c r="BG12" t="n">
-        <v>329</v>
+        <v>58.17489289431744</v>
       </c>
       <c r="BH12" t="n">
-        <v>329</v>
+        <v>58.25407576942579</v>
       </c>
       <c r="BI12" t="n">
-        <v>329</v>
+        <v>59.49691453769827</v>
       </c>
       <c r="BJ12" t="n">
-        <v>329</v>
+        <v>59.80023745772252</v>
       </c>
       <c r="BK12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BL12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BM12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BN12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BO12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BP12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BQ12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BR12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BS12" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.631578947368421</v>
+        <v>669</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.76</v>
+        <v>669</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.9696969696969697</v>
+        <v>669</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.8461538461538461</v>
+        <v>669</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.7173913043478261</v>
+        <v>669</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.7173913043478261</v>
+        <v>669</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.7173913043478261</v>
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>475.07</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>47.86</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>479</v>
       </c>
       <c r="C13" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D13" t="n">
         <v>39</v>
-      </c>
-      <c r="D13" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E13" t="n">
         <v>479</v>
@@ -3558,720 +3976,819 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>493.0388949463128</v>
-      </c>
-      <c r="J13" t="n">
-        <v>49.6067698461252</v>
-      </c>
-      <c r="K13" t="n">
-        <v>490.4169243248012</v>
-      </c>
-      <c r="L13" t="n">
-        <v>52.37872954981898</v>
-      </c>
-      <c r="M13" t="n">
-        <v>482.3143468988038</v>
-      </c>
-      <c r="N13" t="n">
-        <v>58.05545820133912</v>
-      </c>
-      <c r="O13" t="n">
-        <v>473.6445893214021</v>
-      </c>
-      <c r="P13" t="n">
-        <v>55.5076480972392</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>469.8768147608204</v>
-      </c>
       <c r="R13" t="n">
-        <v>53.89154980530927</v>
+        <v>493.04</v>
       </c>
       <c r="S13" t="n">
-        <v>474.6352617009007</v>
+        <v>49.61</v>
       </c>
       <c r="T13" t="n">
-        <v>53.22848453774547</v>
+        <v>490.42</v>
       </c>
       <c r="U13" t="n">
-        <v>476.8488439169188</v>
+        <v>52.38</v>
       </c>
       <c r="V13" t="n">
-        <v>49.48734341479344</v>
+        <v>482.31</v>
       </c>
       <c r="W13" t="n">
-        <v>478.1346701765436</v>
+        <v>58.06</v>
       </c>
       <c r="X13" t="n">
-        <v>47.71987784086954</v>
+        <v>473.64</v>
       </c>
       <c r="Y13" t="n">
-        <v>480.1593109971819</v>
+        <v>55.51</v>
       </c>
       <c r="Z13" t="n">
-        <v>45.51259221148141</v>
+        <v>469.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>53.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>474.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>53.23</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>476.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>49.49</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>478.13</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>47.72</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>480.16</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>45.51</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>494.05</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>491.1</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>490.45</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>489.04</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>487.2166666666666</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>485.4285714285714</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>484.75625</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>483.9611111111111</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>483.105</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>82.558751807425</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>77.80696198498778</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>74.34697371110676</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>71.80973750126093</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>69.0601408596562</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>67.16431268135767</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>66.45230873293643</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>65.17483869381981</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>64.21342519286758</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>330</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>330</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>330</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>330</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>330</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>330</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>330</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>330</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>330</v>
       </c>
-      <c r="BK13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>669</v>
-      </c>
       <c r="BT13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="BX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY13" t="n">
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
         <v>0.8</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.7837837837837838</v>
       </c>
-      <c r="CA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB13" t="n">
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
         <v>0.6037735849056604</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>480.16</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>45.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S14_G2_478_38_REL2</t>
+          <t>S13_G2_480_39_REL2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D14" t="n">
-        <v>56.33802816901409</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>480.5520796557154</v>
-      </c>
-      <c r="J14" t="n">
-        <v>50.38262739490732</v>
-      </c>
-      <c r="K14" t="n">
-        <v>489.0447203992205</v>
-      </c>
-      <c r="L14" t="n">
-        <v>46.60897787656309</v>
-      </c>
-      <c r="M14" t="n">
-        <v>487.1359851109566</v>
-      </c>
-      <c r="N14" t="n">
-        <v>42.70486691982016</v>
-      </c>
-      <c r="O14" t="n">
-        <v>482.1616171761792</v>
-      </c>
-      <c r="P14" t="n">
-        <v>51.78645811417188</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>483.3317497440513</v>
-      </c>
       <c r="R14" t="n">
-        <v>50.31387403503228</v>
+        <v>470.82</v>
       </c>
       <c r="S14" t="n">
-        <v>489.4445616035464</v>
+        <v>43.33</v>
       </c>
       <c r="T14" t="n">
-        <v>47.42064006557113</v>
+        <v>468.92</v>
       </c>
       <c r="U14" t="n">
-        <v>488.4813093165004</v>
+        <v>47.56</v>
       </c>
       <c r="V14" t="n">
-        <v>45.76361753499361</v>
+        <v>479</v>
       </c>
       <c r="W14" t="n">
-        <v>484.7105552002903</v>
+        <v>50.93</v>
       </c>
       <c r="X14" t="n">
-        <v>47.0577152289614</v>
+        <v>476.41</v>
       </c>
       <c r="Y14" t="n">
-        <v>479.8836726994969</v>
+        <v>49.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>47.78306593376653</v>
+        <v>474.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>44.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>479.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>47.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>480.59</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>47.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>476.68</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>46.51</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>475.58</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>46.34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>476.425</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>480.8333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>483.775</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>484.51</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>485.1083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>486.9214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>487.24375</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>486.0166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>484.31</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>82.41871374269317</v>
+        <v>490.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>75.03069742149245</v>
+        <v>481.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>68.80170328560187</v>
+        <v>479.35</v>
       </c>
       <c r="AV14" t="n">
-        <v>65.61729878621948</v>
+        <v>479.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>63.87067608761386</v>
+        <v>478.875</v>
       </c>
       <c r="AX14" t="n">
-        <v>61.85271305484422</v>
+        <v>480.7428571428571</v>
       </c>
       <c r="AY14" t="n">
-        <v>60.02007444128589</v>
+        <v>482.96875</v>
       </c>
       <c r="AZ14" t="n">
-        <v>59.55142269034758</v>
+        <v>482.55</v>
       </c>
       <c r="BA14" t="n">
-        <v>60.15258847298261</v>
+        <v>481.935</v>
       </c>
       <c r="BB14" t="n">
-        <v>336</v>
+        <v>71.32138529221092</v>
       </c>
       <c r="BC14" t="n">
-        <v>336</v>
+        <v>68.8926217626629</v>
       </c>
       <c r="BD14" t="n">
-        <v>336</v>
+        <v>66.4656114092092</v>
       </c>
       <c r="BE14" t="n">
-        <v>336</v>
+        <v>64.65841012582973</v>
       </c>
       <c r="BF14" t="n">
-        <v>336</v>
+        <v>62.39865950750331</v>
       </c>
       <c r="BG14" t="n">
-        <v>336</v>
+        <v>60.1614935496323</v>
       </c>
       <c r="BH14" t="n">
-        <v>336</v>
+        <v>59.2345361544893</v>
       </c>
       <c r="BI14" t="n">
-        <v>336</v>
+        <v>59.05790708185391</v>
       </c>
       <c r="BJ14" t="n">
-        <v>336</v>
+        <v>58.24071406670766</v>
       </c>
       <c r="BK14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BL14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BM14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BN14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BO14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BP14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BQ14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BR14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BS14" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.2222222222222222</v>
+        <v>669</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.8461538461538461</v>
+        <v>669</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.6818181818181818</v>
+        <v>669</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.7407407407407407</v>
+        <v>669</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.65625</v>
+        <v>669</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.6363636363636364</v>
+        <v>669</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.6176470588235294</v>
+        <v>669</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.6176470588235294</v>
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.5434782608695652</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>475.58</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>46.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S16_G2_482_38_REL2</t>
+          <t>S14_G2_478_38_REL2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C15" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D15" t="n">
         <v>38</v>
       </c>
-      <c r="D15" t="n">
-        <v>56.33802816901409</v>
-      </c>
       <c r="E15" t="n">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>481.9825335954972</v>
-      </c>
-      <c r="J15" t="n">
-        <v>41.2755751049739</v>
-      </c>
-      <c r="K15" t="n">
-        <v>488.4589635384625</v>
-      </c>
-      <c r="L15" t="n">
-        <v>44.18864008638722</v>
-      </c>
-      <c r="M15" t="n">
-        <v>488.8676723389598</v>
-      </c>
-      <c r="N15" t="n">
-        <v>39.56790844132409</v>
-      </c>
-      <c r="O15" t="n">
-        <v>488.8891767134903</v>
-      </c>
-      <c r="P15" t="n">
-        <v>42.95237286881233</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>488.9957121883287</v>
-      </c>
       <c r="R15" t="n">
-        <v>39.67702099844163</v>
+        <v>480.55</v>
       </c>
       <c r="S15" t="n">
-        <v>488.9986954275019</v>
+        <v>50.38</v>
       </c>
       <c r="T15" t="n">
-        <v>39.56528665778695</v>
+        <v>489.04</v>
       </c>
       <c r="U15" t="n">
-        <v>487.5581750046007</v>
+        <v>46.61</v>
       </c>
       <c r="V15" t="n">
-        <v>39.66143568539886</v>
+        <v>487.14</v>
       </c>
       <c r="W15" t="n">
-        <v>486.0724860364916</v>
+        <v>42.7</v>
       </c>
       <c r="X15" t="n">
-        <v>41.58978775647055</v>
+        <v>482.16</v>
       </c>
       <c r="Y15" t="n">
-        <v>486.205703468019</v>
+        <v>51.79</v>
       </c>
       <c r="Z15" t="n">
-        <v>40.91749429091345</v>
+        <v>483.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>50.31</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>489.44</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>47.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>488.48</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>45.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>484.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>47.06</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>479.88</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>47.78</v>
       </c>
       <c r="AJ15" t="n">
-        <v>477.075</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>479.95</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>482.125</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>483.54</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>484.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>485.375</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>485.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>485.63</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>83.69599378106457</v>
+        <v>476.425</v>
       </c>
       <c r="AT15" t="n">
-        <v>74.56304379516705</v>
+        <v>480.8333333333333</v>
       </c>
       <c r="AU15" t="n">
-        <v>68.59944879516161</v>
+        <v>483.775</v>
       </c>
       <c r="AV15" t="n">
-        <v>64.67030539590795</v>
+        <v>484.51</v>
       </c>
       <c r="AW15" t="n">
-        <v>61.67079040266056</v>
+        <v>485.1083333333333</v>
       </c>
       <c r="AX15" t="n">
-        <v>59.27586837346688</v>
+        <v>486.9214285714286</v>
       </c>
       <c r="AY15" t="n">
-        <v>56.94720691131392</v>
+        <v>487.24375</v>
       </c>
       <c r="AZ15" t="n">
-        <v>55.37721374779645</v>
+        <v>486.0166666666667</v>
       </c>
       <c r="BA15" t="n">
-        <v>53.90151296577861</v>
+        <v>484.31</v>
       </c>
       <c r="BB15" t="n">
-        <v>323</v>
+        <v>82.41871374269317</v>
       </c>
       <c r="BC15" t="n">
-        <v>323</v>
+        <v>75.03069742149245</v>
       </c>
       <c r="BD15" t="n">
-        <v>323</v>
+        <v>68.80170328560187</v>
       </c>
       <c r="BE15" t="n">
-        <v>323</v>
+        <v>65.61729878621948</v>
       </c>
       <c r="BF15" t="n">
-        <v>323</v>
+        <v>63.87067608761386</v>
       </c>
       <c r="BG15" t="n">
-        <v>323</v>
+        <v>61.85271305484422</v>
       </c>
       <c r="BH15" t="n">
-        <v>323</v>
+        <v>60.02007444128589</v>
       </c>
       <c r="BI15" t="n">
-        <v>323</v>
+        <v>59.55142269034758</v>
       </c>
       <c r="BJ15" t="n">
-        <v>323</v>
+        <v>60.15258847298261</v>
       </c>
       <c r="BK15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BL15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BM15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BN15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BO15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BP15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BQ15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BR15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BS15" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.6428571428571429</v>
+        <v>669</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.5294117647058824</v>
+        <v>669</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.6274509803921569</v>
+        <v>669</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.7358490566037735</v>
+        <v>669</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.8363636363636363</v>
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>479.88</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>47.78</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>478</v>
       </c>
       <c r="C16" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D16" t="n">
         <v>40</v>
-      </c>
-      <c r="D16" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E16" t="n">
         <v>478</v>
@@ -4296,474 +4813,540 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>458.3216721408576</v>
-      </c>
-      <c r="J16" t="n">
-        <v>45.16436633974698</v>
-      </c>
-      <c r="K16" t="n">
-        <v>461.5523719799152</v>
-      </c>
-      <c r="L16" t="n">
-        <v>46.53143054793183</v>
-      </c>
-      <c r="M16" t="n">
-        <v>456.0162445803919</v>
-      </c>
-      <c r="N16" t="n">
-        <v>41.18067482486174</v>
-      </c>
-      <c r="O16" t="n">
-        <v>460.8667428230174</v>
-      </c>
-      <c r="P16" t="n">
-        <v>44.7540939374308</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>461.8525274095288</v>
-      </c>
       <c r="R16" t="n">
-        <v>49.79068015904434</v>
+        <v>458.32</v>
       </c>
       <c r="S16" t="n">
-        <v>465.9751313912141</v>
+        <v>45.16</v>
       </c>
       <c r="T16" t="n">
-        <v>46.42402202578488</v>
+        <v>461.55</v>
       </c>
       <c r="U16" t="n">
-        <v>467.2341391319979</v>
+        <v>46.53</v>
       </c>
       <c r="V16" t="n">
-        <v>43.87524415332425</v>
+        <v>456.02</v>
       </c>
       <c r="W16" t="n">
-        <v>466.9737652304451</v>
+        <v>41.18</v>
       </c>
       <c r="X16" t="n">
-        <v>40.91797539007516</v>
+        <v>460.87</v>
       </c>
       <c r="Y16" t="n">
-        <v>469.2605909259337</v>
+        <v>44.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>41.43172339056864</v>
+        <v>461.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>49.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>465.98</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>46.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>467.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>43.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>466.97</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>40.92</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>469.26</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>41.43</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>478.075</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>473.95</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>472.3375</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>470.71</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>469.9083333333334</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>471.0357142857143</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>471.5375</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>472.8833333333333</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>473.94</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>85.57551854940758</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>77.16420262444669</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>71.75948434701854</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>68.53747806857209</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>66.68558012960689</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>65.88977925447983</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>64.14513694544583</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>61.97752953019882</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>59.99338630215834</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>335</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>335</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>335</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>335</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>335</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>335</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>335</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>335</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>335</v>
       </c>
-      <c r="BK16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>669</v>
-      </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.918918918918919</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.95</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.9302325581395349</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.8888888888888888</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>469.26</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>41.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S13_G2_480_39_REL2</t>
+          <t>S16_G2_482_38_REL2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D17" t="n">
-        <v>57.82060785767235</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>470.8195308427913</v>
-      </c>
-      <c r="J17" t="n">
-        <v>43.33265912428488</v>
-      </c>
-      <c r="K17" t="n">
-        <v>468.9211195588206</v>
-      </c>
-      <c r="L17" t="n">
-        <v>47.55610849302008</v>
-      </c>
-      <c r="M17" t="n">
-        <v>479.0025310531364</v>
-      </c>
-      <c r="N17" t="n">
-        <v>50.93313391342362</v>
-      </c>
-      <c r="O17" t="n">
-        <v>476.4112012125231</v>
-      </c>
-      <c r="P17" t="n">
-        <v>49.14603141956016</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>474.8491382945342</v>
-      </c>
       <c r="R17" t="n">
-        <v>44.06773500047816</v>
+        <v>481.98</v>
       </c>
       <c r="S17" t="n">
-        <v>479.3396679919038</v>
+        <v>41.28</v>
       </c>
       <c r="T17" t="n">
-        <v>47.08832558201102</v>
+        <v>488.46</v>
       </c>
       <c r="U17" t="n">
-        <v>480.5859219811188</v>
+        <v>44.19</v>
       </c>
       <c r="V17" t="n">
-        <v>47.89324913188214</v>
+        <v>488.87</v>
       </c>
       <c r="W17" t="n">
-        <v>476.68209433003</v>
+        <v>39.57</v>
       </c>
       <c r="X17" t="n">
-        <v>46.50655975949061</v>
+        <v>488.89</v>
       </c>
       <c r="Y17" t="n">
-        <v>475.5775721943007</v>
+        <v>42.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>46.34173487651728</v>
+        <v>489</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>39.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>39.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>487.56</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>39.66</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>486.07</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>41.59</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>486.21</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>40.92</v>
       </c>
       <c r="AJ17" t="n">
-        <v>490.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>481.8</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>479.35</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>479.1</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>478.875</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>480.7428571428571</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>482.96875</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>482.55</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>481.935</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>71.32138529221092</v>
+        <v>477.075</v>
       </c>
       <c r="AT17" t="n">
-        <v>68.8926217626629</v>
+        <v>479.95</v>
       </c>
       <c r="AU17" t="n">
-        <v>66.4656114092092</v>
+        <v>482.125</v>
       </c>
       <c r="AV17" t="n">
-        <v>64.65841012582973</v>
+        <v>483.54</v>
       </c>
       <c r="AW17" t="n">
-        <v>62.39865950750331</v>
+        <v>484.3833333333333</v>
       </c>
       <c r="AX17" t="n">
-        <v>60.1614935496323</v>
+        <v>485</v>
       </c>
       <c r="AY17" t="n">
-        <v>59.2345361544893</v>
+        <v>485.375</v>
       </c>
       <c r="AZ17" t="n">
-        <v>59.05790708185391</v>
+        <v>485.4444444444445</v>
       </c>
       <c r="BA17" t="n">
-        <v>58.24071406670766</v>
+        <v>485.63</v>
       </c>
       <c r="BB17" t="n">
-        <v>342</v>
+        <v>83.69599378106457</v>
       </c>
       <c r="BC17" t="n">
-        <v>342</v>
+        <v>74.56304379516705</v>
       </c>
       <c r="BD17" t="n">
-        <v>342</v>
+        <v>68.59944879516161</v>
       </c>
       <c r="BE17" t="n">
-        <v>342</v>
+        <v>64.67030539590795</v>
       </c>
       <c r="BF17" t="n">
-        <v>342</v>
+        <v>61.67079040266056</v>
       </c>
       <c r="BG17" t="n">
-        <v>342</v>
+        <v>59.27586837346688</v>
       </c>
       <c r="BH17" t="n">
-        <v>342</v>
+        <v>56.94720691131392</v>
       </c>
       <c r="BI17" t="n">
-        <v>342</v>
+        <v>55.37721374779645</v>
       </c>
       <c r="BJ17" t="n">
-        <v>342</v>
+        <v>53.90151296577861</v>
       </c>
       <c r="BK17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BL17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BM17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BN17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BO17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BP17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BQ17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BR17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BS17" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BT17" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.4375</v>
+        <v>669</v>
       </c>
       <c r="BV17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CE17" t="n">
         <v>0.5</v>
       </c>
-      <c r="BW17" t="n">
-        <v>0.4848484848484849</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0.119047619047619</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0.4347826086956522</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0.4347826086956522</v>
-      </c>
-      <c r="CA17" t="n">
+      <c r="CF17" t="n">
         <v>0.5</v>
       </c>
-      <c r="CB17" t="n">
-        <v>0.5434782608695652</v>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.6274509803921569</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.7358490566037735</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.8363636363636363</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>486.21</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>40.92</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>482</v>
       </c>
       <c r="C18" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D18" t="n">
         <v>41</v>
-      </c>
-      <c r="D18" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E18" t="n">
         <v>482</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>488.3994767223659</v>
-      </c>
-      <c r="J18" t="n">
-        <v>29.64775805136673</v>
-      </c>
-      <c r="K18" t="n">
-        <v>499.4406005194213</v>
-      </c>
-      <c r="L18" t="n">
-        <v>31.83886312745928</v>
-      </c>
-      <c r="M18" t="n">
-        <v>488.8648182732567</v>
-      </c>
-      <c r="N18" t="n">
-        <v>44.76618292257717</v>
-      </c>
-      <c r="O18" t="n">
-        <v>489.4188082018974</v>
-      </c>
-      <c r="P18" t="n">
-        <v>43.75833425683095</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>493.0511230068881</v>
-      </c>
       <c r="R18" t="n">
-        <v>42.98063310636479</v>
+        <v>488.4</v>
       </c>
       <c r="S18" t="n">
-        <v>488.5310523653769</v>
+        <v>29.65</v>
       </c>
       <c r="T18" t="n">
-        <v>48.066355326625</v>
+        <v>499.44</v>
       </c>
       <c r="U18" t="n">
-        <v>486.5000907605244</v>
+        <v>31.84</v>
       </c>
       <c r="V18" t="n">
-        <v>49.28314977605542</v>
+        <v>488.86</v>
       </c>
       <c r="W18" t="n">
-        <v>486.2211764386664</v>
+        <v>44.77</v>
       </c>
       <c r="X18" t="n">
-        <v>51.40353439618929</v>
+        <v>489.42</v>
       </c>
       <c r="Y18" t="n">
-        <v>482.8895845682731</v>
+        <v>43.76</v>
       </c>
       <c r="Z18" t="n">
-        <v>55.51369428792032</v>
+        <v>493.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>42.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>488.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>48.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>486.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>49.28</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>486.22</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>51.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>482.89</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>55.51</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>490.175</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>493.3166666666667</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>491.225</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>488.66</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>488.4666666666666</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>487.8428571428572</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>487.33125</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>487</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>485.805</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>71.90441137371198</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>62.86347420314032</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>60.72622477151037</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>60.26611319804854</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>59.00126175675305</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>58.07080301894667</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>57.07448224414743</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>56.23976450085038</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>57.27370229869901</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>325</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>325</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>325</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>325</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>325</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>325</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>325</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>325</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>325</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.85</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.5666666666666667</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.45</v>
       </c>
-      <c r="BY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ18" t="n">
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
         <v>0.456140350877193</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.4918032786885246</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.463768115942029</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>482.89</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>55.51</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>481</v>
       </c>
       <c r="C19" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D19" t="n">
         <v>41</v>
-      </c>
-      <c r="D19" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E19" t="n">
         <v>481</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>447.0560960233428</v>
-      </c>
-      <c r="J19" t="n">
-        <v>35.74202855158483</v>
-      </c>
-      <c r="K19" t="n">
-        <v>462.7608990789693</v>
-      </c>
-      <c r="L19" t="n">
-        <v>40.96271541507575</v>
-      </c>
-      <c r="M19" t="n">
-        <v>459.8300681595151</v>
-      </c>
-      <c r="N19" t="n">
-        <v>39.83112239033291</v>
-      </c>
-      <c r="O19" t="n">
-        <v>459.5461682476358</v>
-      </c>
-      <c r="P19" t="n">
-        <v>50.56601957842931</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>465.2394601757011</v>
-      </c>
       <c r="R19" t="n">
-        <v>51.23993810071873</v>
+        <v>447.06</v>
       </c>
       <c r="S19" t="n">
-        <v>472.0140937976486</v>
+        <v>35.74</v>
       </c>
       <c r="T19" t="n">
-        <v>50.69688946598301</v>
+        <v>462.76</v>
       </c>
       <c r="U19" t="n">
-        <v>473.9521470867909</v>
+        <v>40.96</v>
       </c>
       <c r="V19" t="n">
-        <v>52.05084566746809</v>
+        <v>459.83</v>
       </c>
       <c r="W19" t="n">
-        <v>475.2162438410218</v>
+        <v>39.83</v>
       </c>
       <c r="X19" t="n">
-        <v>50.98999056258803</v>
+        <v>459.55</v>
       </c>
       <c r="Y19" t="n">
-        <v>475.196695048263</v>
+        <v>50.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>47.92617876062318</v>
+        <v>465.24</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>51.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>472.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>50.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>473.95</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>52.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>475.22</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>50.99</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>475.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>47.93</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>473.05</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>469.1166666666667</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>469.775</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>467.86</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>467.9583333333333</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>472.2</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>475.2375</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>478.6333333333333</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>480.12</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>84.17866416141325</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>74.89839599231895</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>67.93470670430543</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>65.35380937634777</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>64.4126534972404</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>63.66409618346233</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>63.87639308656994</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>63.6001310271187</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>64.22387095153951</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>325</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>325</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>325</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>325</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>325</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>325</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>325</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>325</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>325</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>1</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.4838709677419355</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.6129032258064516</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.6774193548387096</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.967741935483871</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>475.2</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>47.93</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>482</v>
       </c>
       <c r="C20" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D20" t="n">
         <v>38</v>
-      </c>
-      <c r="D20" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E20" t="n">
         <v>482</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>470.4271360025415</v>
-      </c>
-      <c r="J20" t="n">
-        <v>49.50752976649605</v>
-      </c>
-      <c r="K20" t="n">
-        <v>477.010397195163</v>
-      </c>
-      <c r="L20" t="n">
-        <v>55.97769107541174</v>
-      </c>
-      <c r="M20" t="n">
-        <v>477.7423739978739</v>
-      </c>
-      <c r="N20" t="n">
-        <v>44.8491674188218</v>
-      </c>
-      <c r="O20" t="n">
-        <v>482.4958665941476</v>
-      </c>
-      <c r="P20" t="n">
-        <v>45.91636748160431</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>486.1113191323481</v>
-      </c>
       <c r="R20" t="n">
-        <v>50.31836879244808</v>
+        <v>470.43</v>
       </c>
       <c r="S20" t="n">
-        <v>486.2857951197687</v>
+        <v>49.51</v>
       </c>
       <c r="T20" t="n">
-        <v>46.80623665585281</v>
+        <v>477.01</v>
       </c>
       <c r="U20" t="n">
-        <v>486.5540190727731</v>
+        <v>55.98</v>
       </c>
       <c r="V20" t="n">
-        <v>44.49632164043845</v>
+        <v>477.74</v>
       </c>
       <c r="W20" t="n">
-        <v>486.3671370144896</v>
+        <v>44.85</v>
       </c>
       <c r="X20" t="n">
-        <v>45.82353237549396</v>
+        <v>482.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>488.0875488144652</v>
+        <v>45.92</v>
       </c>
       <c r="Z20" t="n">
-        <v>43.36739385816811</v>
+        <v>486.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>50.32</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>486.29</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>46.81</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>486.55</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>44.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>486.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>45.82</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>488.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>43.37</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>489.575</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>483.9</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>482.8875</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>483.25</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>484.2916666666667</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>484.6571428571428</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>485.075</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>485.1055555555556</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>484.685</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>87.54195779738994</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>80.1707968444038</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>74.4217699584604</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>69.73913893933592</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>66.45354214704352</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>64.67200447848595</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>63.09135737167176</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>61.17756462609676</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>59.50063676129862</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>317</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>317</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>317</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>317</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>317</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>317</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>317</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>317</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>317</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.6</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.5</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.5185185185185185</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.5483870967741935</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.59375</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.671875</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>488.09</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>43.37</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>480</v>
       </c>
       <c r="C21" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D21" t="n">
         <v>41</v>
-      </c>
-      <c r="D21" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E21" t="n">
         <v>480</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>509.9270700856268</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29.4524221558557</v>
-      </c>
-      <c r="K21" t="n">
-        <v>507.7160929695423</v>
-      </c>
-      <c r="L21" t="n">
-        <v>33.96981488961056</v>
-      </c>
-      <c r="M21" t="n">
-        <v>500.7332612269762</v>
-      </c>
-      <c r="N21" t="n">
-        <v>37.0563951473104</v>
-      </c>
-      <c r="O21" t="n">
-        <v>497.4705228345918</v>
-      </c>
-      <c r="P21" t="n">
-        <v>37.71821096909892</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>498.258092862693</v>
-      </c>
       <c r="R21" t="n">
-        <v>34.58240177057341</v>
+        <v>509.93</v>
       </c>
       <c r="S21" t="n">
-        <v>497.1752180325369</v>
+        <v>29.45</v>
       </c>
       <c r="T21" t="n">
-        <v>34.78407348381415</v>
+        <v>507.72</v>
       </c>
       <c r="U21" t="n">
-        <v>498.3977351806348</v>
+        <v>33.97</v>
       </c>
       <c r="V21" t="n">
-        <v>37.24150426732809</v>
+        <v>500.73</v>
       </c>
       <c r="W21" t="n">
-        <v>493.9404787733081</v>
+        <v>37.06</v>
       </c>
       <c r="X21" t="n">
-        <v>37.36225776273827</v>
+        <v>497.47</v>
       </c>
       <c r="Y21" t="n">
-        <v>492.8724609056306</v>
+        <v>37.72</v>
       </c>
       <c r="Z21" t="n">
-        <v>38.88374354313176</v>
+        <v>498.26</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>34.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>497.18</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>34.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>498.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>37.24</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>493.94</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>37.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>492.87</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>38.88</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>506.875</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>505.6833333333333</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>504.475</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>502.44</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>500.0666666666667</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>500.0142857142857</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>498.1375</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>498.0333333333334</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>495.62</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>70.48481662741274</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>63.24568276877788</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>59.48108417808136</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>58.24162085656613</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>57.77913887285695</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>55.24464883126506</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>54.59252324036689</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>52.46352171853421</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>52.28991872244592</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>321</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>321</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>321</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>321</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>321</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>321</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>321</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>321</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>321</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>1</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>1</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.6</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.525</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.5102040816326531</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.5094339622641509</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.5370370370370371</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.5555555555555556</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>492.87</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>38.88</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>480.4</v>
       </c>
       <c r="C22" t="n">
+        <v>58.71015567086731</v>
+      </c>
+      <c r="D22" t="n">
         <v>39.6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>58.71015567086731</v>
       </c>
       <c r="E22" t="n">
         <v>480.4</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.51175</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>80.425</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.335</v>
+      </c>
       <c r="I22" t="n">
-        <v>475.4619580935088</v>
+        <v>2.3005</v>
       </c>
       <c r="J22" t="n">
-        <v>43.41386073926667</v>
+        <v>2.3</v>
       </c>
       <c r="K22" t="n">
-        <v>480.9371920703246</v>
+        <v>2.351</v>
       </c>
       <c r="L22" t="n">
-        <v>46.23888772105344</v>
+        <v>2.381</v>
       </c>
       <c r="M22" t="n">
-        <v>479.7863430219157</v>
+        <v>2.398</v>
       </c>
       <c r="N22" t="n">
-        <v>45.94888257477395</v>
+        <v>2.6575</v>
       </c>
       <c r="O22" t="n">
-        <v>479.3555454345906</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>47.02300892437482</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>479.9092690573838</v>
-      </c>
+        <v>2.411499999999999</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>47.0305523018221</v>
+        <v>475.4625</v>
       </c>
       <c r="S22" t="n">
-        <v>481.5113127982668</v>
+        <v>43.4145</v>
       </c>
       <c r="T22" t="n">
-        <v>47.20216137451911</v>
+        <v>480.9369999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>481.7862854121255</v>
+        <v>46.239</v>
       </c>
       <c r="V22" t="n">
-        <v>46.77648001644623</v>
+        <v>479.7855</v>
       </c>
       <c r="W22" t="n">
-        <v>481.6318811000506</v>
+        <v>45.9495</v>
       </c>
       <c r="X22" t="n">
-        <v>46.70407969270074</v>
+        <v>479.3554999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>481.9532001560549</v>
+        <v>47.024</v>
       </c>
       <c r="Z22" t="n">
-        <v>46.38871061371513</v>
+        <v>479.9095</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>47.02950000000001</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>481.513</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>47.20200000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>481.7859999999999</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>46.777</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>481.631</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>46.70350000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>481.9535000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>46.38799999999999</v>
       </c>
       <c r="AJ22" t="n">
-        <v>487.33875</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>484.5841666666666</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>484.21125</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>487.3389999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>484.585</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>484.2115</v>
+      </c>
+      <c r="AV22" t="n">
         <v>483.872</v>
       </c>
-      <c r="AN22" t="n">
-        <v>483.5120833333334</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>483.6103571428572</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>483.9328125</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>484.4586111111112</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>484.5800000000001</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>82.08770157945632</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>74.38011065483015</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>69.38501902112047</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>66.46149630739485</v>
-      </c>
       <c r="AW22" t="n">
-        <v>64.50316708244353</v>
+        <v>483.5125</v>
       </c>
       <c r="AX22" t="n">
-        <v>63.10411101686896</v>
+        <v>483.611</v>
       </c>
       <c r="AY22" t="n">
-        <v>62.05701251831164</v>
+        <v>483.933</v>
       </c>
       <c r="AZ22" t="n">
-        <v>60.96996903638519</v>
+        <v>484.459</v>
       </c>
       <c r="BA22" t="n">
-        <v>60.16129970354324</v>
+        <v>484.5810000000001</v>
       </c>
       <c r="BB22" t="n">
+        <v>82.08750000000001</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>74.379</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>69.38500000000002</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>66.46199999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>64.504</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>63.10300000000001</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>62.05749999999999</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>60.97000000000001</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="BK22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>329.9</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>670.85</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.723015873015873</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.660626782703021</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.6203603040667922</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.6883215185775824</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.6002653342155163</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.6591488400305046</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.676194638058593</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.6535336264447262</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.6949899219505622</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>481.9535000000001</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>46.38799999999999</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.429022485182754</v>
       </c>
       <c r="C23" t="n">
+        <v>2.276566036915978</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.535543791899829</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.276566036915978</v>
       </c>
       <c r="E23" t="n">
         <v>1.429022485182754</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01320635811784772</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.703518031665801</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2344871223037969</v>
+      </c>
       <c r="I23" t="n">
-        <v>15.19284793977868</v>
+        <v>0.1948136761653366</v>
       </c>
       <c r="J23" t="n">
-        <v>10.38906632759833</v>
+        <v>0.1853020294148533</v>
       </c>
       <c r="K23" t="n">
-        <v>13.79748312244704</v>
+        <v>0.1744133022449836</v>
       </c>
       <c r="L23" t="n">
-        <v>8.612847894997751</v>
+        <v>0.1637681287674742</v>
       </c>
       <c r="M23" t="n">
-        <v>13.32971284973741</v>
+        <v>0.1653258345781063</v>
       </c>
       <c r="N23" t="n">
-        <v>6.977785961999453</v>
+        <v>0.192350420354431</v>
       </c>
       <c r="O23" t="n">
-        <v>12.40254028754054</v>
+        <v>0.201337632113977</v>
       </c>
       <c r="P23" t="n">
-        <v>5.009915755915317</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>12.06643394197913</v>
-      </c>
+        <v>0.2199108671113918</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>5.524949967347123</v>
+        <v>15.19331773995951</v>
       </c>
       <c r="S23" t="n">
-        <v>9.924844013314026</v>
+        <v>10.38895236853984</v>
       </c>
       <c r="T23" t="n">
-        <v>5.302936118567024</v>
+        <v>13.79903318504979</v>
       </c>
       <c r="U23" t="n">
-        <v>8.924522619972036</v>
+        <v>8.612995627783084</v>
       </c>
       <c r="V23" t="n">
-        <v>5.104715671331086</v>
+        <v>13.32877475910474</v>
       </c>
       <c r="W23" t="n">
-        <v>7.512324848628649</v>
+        <v>6.978409919172131</v>
       </c>
       <c r="X23" t="n">
-        <v>4.684206886021602</v>
+        <v>12.40231153115376</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.134813262924959</v>
+        <v>5.010116502479863</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.222195965725771</v>
+        <v>12.06676753253374</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>5.524590458743718</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>9.925259694335459</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>5.30374108282863</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>8.92448046549195</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>5.105643008115216</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>7.512810743201097</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>4.684634766418491</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>7.134417893858654</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.222233440326386</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10.75726643948173</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>9.871628486557224</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>9.250714677227583</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>10.75812539921631</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.871358622430435</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9.251440442609898</v>
+      </c>
+      <c r="AV23" t="n">
         <v>8.949032643987726</v>
       </c>
-      <c r="AN23" t="n">
-        <v>8.687916120287872</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>7.859434892963667</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>6.922521429361347</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>6.144192880809933</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>5.391999921911604</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>7.384044366928151</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.53603708623436</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.819212547447287</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.982833539911003</v>
-      </c>
       <c r="AW23" t="n">
-        <v>4.510949424311551</v>
+        <v>8.688121882323316</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.495991389791815</v>
+        <v>7.858719528751417</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.346914555961569</v>
+        <v>6.922798415000741</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.363035939633669</v>
+        <v>6.144711804299261</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.450977181940732</v>
+        <v>5.392350234603793</v>
       </c>
       <c r="BB23" t="n">
+        <v>7.385887592315211</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>6.53629937148569</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.819106008386692</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.983140628791825</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.510819041044835</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.496697150482552</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.347289385352672</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>4.362663358425374</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4.451751872784703</v>
+      </c>
+      <c r="BK23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>7.107446058443512</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>8.273451516749223</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.229116168344119</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2279240284206699</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.267342709397982</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1670833583359263</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2904252512646689</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2366443451540359</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.1769418666207576</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2347763011372528</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1670452744858719</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>7.134417893858654</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>5.222233440326386</v>
       </c>
     </row>
   </sheetData>
